--- a/results/5153_gauss.xlsx
+++ b/results/5153_gauss.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,99 +413,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>5153</t>
-        </is>
+      <c r="A1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B1" t="n">
+        <v>11.88051200089198</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>0.341</v>
       </c>
       <c r="B2" t="n">
-        <v>752.2419962072357</v>
+        <v>11.77926875903428</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.186</v>
+        <v>0.6819999999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>731.3760688007802</v>
+        <v>10.50238712185229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.372</v>
+        <v>1.023</v>
       </c>
       <c r="B4" t="n">
-        <v>675.3977281679256</v>
+        <v>8.673001450666185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.5735</v>
+        <v>1.364</v>
       </c>
       <c r="B5" t="n">
-        <v>578.5486041075668</v>
+        <v>6.666560902709706</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.7595</v>
+        <v>1.705</v>
       </c>
       <c r="B6" t="n">
-        <v>459.9434794804209</v>
+        <v>4.520743902844142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.961</v>
+        <v>2.046</v>
       </c>
       <c r="B7" t="n">
-        <v>317.9747736018069</v>
+        <v>2.814522333000653</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.147</v>
+        <v>2.387</v>
       </c>
       <c r="B8" t="n">
-        <v>191.8758918009861</v>
+        <v>1.522910362301926</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.3485</v>
+        <v>2.728</v>
       </c>
       <c r="B9" t="n">
-        <v>86.09877134956666</v>
+        <v>0.7119160833722958</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.5345</v>
+        <v>3.069</v>
       </c>
       <c r="B10" t="n">
-        <v>29.40105610787364</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1.736</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3.751309531058398</v>
+        <v>0.3117012869967862</v>
       </c>
     </row>
   </sheetData>

--- a/results/5153_gauss.xlsx
+++ b/results/5153_gauss.xlsx
@@ -413,90 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B1" t="n">
-        <v>11.88051200089198</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="B2" t="n">
-        <v>11.77926875903428</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.6819999999999999</v>
-      </c>
-      <c r="B3" t="n">
-        <v>10.50238712185229</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1.023</v>
-      </c>
-      <c r="B4" t="n">
-        <v>8.673001450666185</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1.364</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6.666560902709706</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1.705</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4.520743902844142</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2.046</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2.814522333000653</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2.387</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1.522910362301926</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.7119160833722958</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>3.069</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.3117012869967862</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/5153_gauss.xlsx
+++ b/results/5153_gauss.xlsx
@@ -413,9 +413,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>-2.387</v>
+      </c>
+      <c r="B1" t="n">
+        <v>11.58132090941997</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>-2.1235</v>
+      </c>
+      <c r="B2" t="n">
+        <v>24.20316089422463</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="B3" t="n">
+        <v>46.77976584644314</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>-1.5965</v>
+      </c>
+      <c r="B4" t="n">
+        <v>82.6608701053681</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>-1.333</v>
+      </c>
+      <c r="B5" t="n">
+        <v>130.8536611818613</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>-1.0695</v>
+      </c>
+      <c r="B6" t="n">
+        <v>187.1635754552499</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>-0.806</v>
+      </c>
+      <c r="B7" t="n">
+        <v>244.3641518213058</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>-0.5425</v>
+      </c>
+      <c r="B8" t="n">
+        <v>293.9163533560656</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>-0.279</v>
+      </c>
+      <c r="B9" t="n">
+        <v>327.128397556723</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>339.3149757895563</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="B11" t="n">
+        <v>330.6789677776383</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="B12" t="n">
+        <v>305.5781428311022</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.6819999999999999</v>
+      </c>
+      <c r="B13" t="n">
+        <v>264.9474552928544</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.9145</v>
+      </c>
+      <c r="B14" t="n">
+        <v>213.0977564984493</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="B15" t="n">
+        <v>156.470634708007</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1.3795</v>
+      </c>
+      <c r="B16" t="n">
+        <v>102.8408415474392</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1.612</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58.77548184713661</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1.8445</v>
+      </c>
+      <c r="B18" t="n">
+        <v>28.43403536244432</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2.077</v>
+      </c>
+      <c r="B19" t="n">
+        <v>11.59347130162995</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/5153_gauss.xlsx
+++ b/results/5153_gauss.xlsx
@@ -418,74 +418,74 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>-2.387</v>
+        <v>-2.976</v>
       </c>
       <c r="B1" t="n">
-        <v>11.58132090941997</v>
+        <v>0.4605932257133862</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-2.1235</v>
+        <v>-2.6505</v>
       </c>
       <c r="B2" t="n">
-        <v>24.20316089422463</v>
+        <v>1.160530964107766</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1.86</v>
+        <v>-2.325</v>
       </c>
       <c r="B3" t="n">
-        <v>46.77976584644314</v>
+        <v>2.288917534799555</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-1.5965</v>
+        <v>-1.984</v>
       </c>
       <c r="B4" t="n">
-        <v>82.6608701053681</v>
+        <v>3.924168008672698</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-1.333</v>
+        <v>-1.6585</v>
       </c>
       <c r="B5" t="n">
-        <v>130.8536611818613</v>
+        <v>5.595960802343758</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.0695</v>
+        <v>-1.333</v>
       </c>
       <c r="B6" t="n">
-        <v>187.1635754552499</v>
+        <v>7.09373619785151</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.806</v>
+        <v>-0.992</v>
       </c>
       <c r="B7" t="n">
-        <v>244.3641518213058</v>
+        <v>8.558085668225354</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.5425</v>
+        <v>-0.6665</v>
       </c>
       <c r="B8" t="n">
-        <v>293.9163533560656</v>
+        <v>9.55226846047877</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.279</v>
+        <v>-0.341</v>
       </c>
       <c r="B9" t="n">
-        <v>327.128397556723</v>
+        <v>10.09828158064496</v>
       </c>
     </row>
     <row r="10">
@@ -493,79 +493,79 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>339.3149757895563</v>
+        <v>10.25581482082279</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.217</v>
+        <v>0.3255</v>
       </c>
       <c r="B11" t="n">
-        <v>330.6789677776383</v>
+        <v>10.18153870495058</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.4495</v>
+        <v>0.651</v>
       </c>
       <c r="B12" t="n">
-        <v>305.5781428311022</v>
+        <v>9.495773209883401</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.992</v>
       </c>
       <c r="B13" t="n">
-        <v>264.9474552928544</v>
+        <v>7.926088346611537</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.9145</v>
+        <v>1.3175</v>
       </c>
       <c r="B14" t="n">
-        <v>213.0977564984493</v>
+        <v>6.484140660581408</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.147</v>
+        <v>1.6585</v>
       </c>
       <c r="B15" t="n">
-        <v>156.470634708007</v>
+        <v>4.767851256979535</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.3795</v>
+        <v>1.984</v>
       </c>
       <c r="B16" t="n">
-        <v>102.8408415474392</v>
+        <v>3.14353041716718</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.612</v>
+        <v>2.325</v>
       </c>
       <c r="B17" t="n">
-        <v>58.77548184713661</v>
+        <v>1.862343078146943</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1.8445</v>
+        <v>2.6505</v>
       </c>
       <c r="B18" t="n">
-        <v>28.43403536244432</v>
+        <v>1.116436922963089</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.077</v>
+        <v>2.9915</v>
       </c>
       <c r="B19" t="n">
-        <v>11.59347130162995</v>
+        <v>0.4495966103456042</v>
       </c>
     </row>
   </sheetData>
